--- a/artfynd/A 15219-2025 artfynd.xlsx
+++ b/artfynd/A 15219-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128704642</v>
       </c>
       <c r="B2" t="n">
-        <v>92248</v>
+        <v>92249</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>128704538</v>
       </c>
       <c r="B3" t="n">
-        <v>92248</v>
+        <v>92249</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 15219-2025 artfynd.xlsx
+++ b/artfynd/A 15219-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128704642</v>
       </c>
       <c r="B2" t="n">
-        <v>92249</v>
+        <v>92276</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>128704538</v>
       </c>
       <c r="B3" t="n">
-        <v>92249</v>
+        <v>92276</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 15219-2025 artfynd.xlsx
+++ b/artfynd/A 15219-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128704642</v>
       </c>
       <c r="B2" t="n">
-        <v>92276</v>
+        <v>92281</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>128704538</v>
       </c>
       <c r="B3" t="n">
-        <v>92276</v>
+        <v>92281</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 15219-2025 artfynd.xlsx
+++ b/artfynd/A 15219-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128704642</v>
       </c>
       <c r="B2" t="n">
-        <v>92281</v>
+        <v>92286</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>128704538</v>
       </c>
       <c r="B3" t="n">
-        <v>92281</v>
+        <v>92286</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 15219-2025 artfynd.xlsx
+++ b/artfynd/A 15219-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128704642</v>
       </c>
       <c r="B2" t="n">
-        <v>92286</v>
+        <v>92290</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>128704538</v>
       </c>
       <c r="B3" t="n">
-        <v>92286</v>
+        <v>92290</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 15219-2025 artfynd.xlsx
+++ b/artfynd/A 15219-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128704642</v>
       </c>
       <c r="B2" t="n">
-        <v>92290</v>
+        <v>92295</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>128704538</v>
       </c>
       <c r="B3" t="n">
-        <v>92290</v>
+        <v>92295</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 15219-2025 artfynd.xlsx
+++ b/artfynd/A 15219-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128704642</v>
       </c>
       <c r="B2" t="n">
-        <v>92303</v>
+        <v>92308</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>128704538</v>
       </c>
       <c r="B3" t="n">
-        <v>92303</v>
+        <v>92308</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 15219-2025 artfynd.xlsx
+++ b/artfynd/A 15219-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128704642</v>
       </c>
       <c r="B2" t="n">
-        <v>92308</v>
+        <v>92311</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>128704538</v>
       </c>
       <c r="B3" t="n">
-        <v>92308</v>
+        <v>92311</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 15219-2025 artfynd.xlsx
+++ b/artfynd/A 15219-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128704642</v>
       </c>
       <c r="B2" t="n">
-        <v>92311</v>
+        <v>92318</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>128704538</v>
       </c>
       <c r="B3" t="n">
-        <v>92311</v>
+        <v>92318</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 15219-2025 artfynd.xlsx
+++ b/artfynd/A 15219-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128704642</v>
       </c>
       <c r="B2" t="n">
-        <v>92318</v>
+        <v>92327</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>128704538</v>
       </c>
       <c r="B3" t="n">
-        <v>92318</v>
+        <v>92327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 15219-2025 artfynd.xlsx
+++ b/artfynd/A 15219-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128704642</v>
+        <v>128704538</v>
       </c>
       <c r="B2" t="n">
-        <v>92327</v>
+        <v>92716</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -713,10 +713,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>432252</v>
+        <v>432251</v>
       </c>
       <c r="R2" t="n">
-        <v>6649195</v>
+        <v>6649309</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -766,6 +766,11 @@
           <t>Granskog i branter</t>
         </is>
       </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>I ytterkant av stort källdråg i sluttningen ned mot Ullen.</t>
+        </is>
+      </c>
       <c r="AJ2" t="inlineStr">
         <is>
           <t>asp</t>
@@ -778,12 +783,12 @@
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>Grov asp med stamskada.</t>
+          <t>Grov äldre asp med stamskada.</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Populus tremula # Grov asp med stamskada.</t>
+          <t>Populus tremula # Grov äldre asp med stamskada.</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -801,10 +806,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128704538</v>
+        <v>128704642</v>
       </c>
       <c r="B3" t="n">
-        <v>92327</v>
+        <v>92716</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -839,10 +844,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>432251</v>
+        <v>432252</v>
       </c>
       <c r="R3" t="n">
-        <v>6649309</v>
+        <v>6649195</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -892,11 +897,6 @@
           <t>Granskog i branter</t>
         </is>
       </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>I ytterkant av stort källdråg i sluttningen ned mot Ullen.</t>
-        </is>
-      </c>
       <c r="AJ3" t="inlineStr">
         <is>
           <t>asp</t>
@@ -909,12 +909,12 @@
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>Grov äldre asp med stamskada.</t>
+          <t>Grov asp med stamskada.</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Populus tremula # Grov äldre asp med stamskada.</t>
+          <t>Populus tremula # Grov asp med stamskada.</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>

--- a/artfynd/A 15219-2025 artfynd.xlsx
+++ b/artfynd/A 15219-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -803,6 +808,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128704538</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -929,8 +939,17 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128704642</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>